--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_LASSO\LAS_Simulation_Jateng\I-O_Analysis\Regional-Economy---Jawa-Tengah\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3AC4E94-0027-4749-8D61-ACF944C8CF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{096EDC42-F7B0-49C2-ACC4-A602AA5AD75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{6004D651-5FD1-4A47-B3D1-E1DB32589301}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6004D651-5FD1-4A47-B3D1-E1DB32589301}"/>
   </bookViews>
   <sheets>
     <sheet name="SType3" sheetId="1" r:id="rId1"/>
@@ -36,10 +36,6 @@
     </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -238,7 +234,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A33DC9-E3CC-4C63-BB30-F93F101A1549}">
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:V13"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -285,96 +281,844 @@
         <v>0.2</v>
       </c>
       <c r="O1">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="P1">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="Q1">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="R1">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="S1">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="T1">
-        <v>0.4</v>
+        <v>0.9</v>
       </c>
       <c r="U1">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="V1">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="2" spans="1:22">
       <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0.1</v>
+      </c>
+      <c r="H2">
+        <v>0.1</v>
+      </c>
+      <c r="I2">
+        <v>0.1</v>
+      </c>
+      <c r="J2">
+        <v>0.1</v>
+      </c>
+      <c r="K2">
+        <v>0.1</v>
+      </c>
+      <c r="L2">
+        <v>0.2</v>
+      </c>
+      <c r="M2">
+        <v>0.2</v>
+      </c>
+      <c r="N2">
+        <v>0.2</v>
+      </c>
+      <c r="O2">
+        <v>0.7</v>
+      </c>
+      <c r="P2">
+        <v>0.7</v>
+      </c>
+      <c r="Q2">
+        <v>0.7</v>
+      </c>
+      <c r="R2">
+        <v>0.9</v>
+      </c>
+      <c r="S2">
+        <v>0.9</v>
+      </c>
+      <c r="T2">
+        <v>0.9</v>
+      </c>
+      <c r="U2">
+        <v>0.9</v>
+      </c>
+      <c r="V2">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
+      <c r="A3">
+        <v>7</v>
+      </c>
+      <c r="B3">
+        <v>26</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <v>0.1</v>
+      </c>
+      <c r="H3">
+        <v>0.1</v>
+      </c>
+      <c r="I3">
+        <v>0.1</v>
+      </c>
+      <c r="J3">
+        <v>0.1</v>
+      </c>
+      <c r="K3">
+        <v>0.1</v>
+      </c>
+      <c r="L3">
+        <v>0.2</v>
+      </c>
+      <c r="M3">
+        <v>0.2</v>
+      </c>
+      <c r="N3">
+        <v>0.2</v>
+      </c>
+      <c r="O3">
+        <v>0.7</v>
+      </c>
+      <c r="P3">
+        <v>0.7</v>
+      </c>
+      <c r="Q3">
+        <v>0.7</v>
+      </c>
+      <c r="R3">
+        <v>0.9</v>
+      </c>
+      <c r="S3">
+        <v>0.9</v>
+      </c>
+      <c r="T3">
+        <v>0.9</v>
+      </c>
+      <c r="U3">
+        <v>0.9</v>
+      </c>
+      <c r="V3">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
+      <c r="A4">
         <v>8</v>
       </c>
-      <c r="B2">
+      <c r="B4">
         <v>24</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0.1</v>
-      </c>
-      <c r="H2">
-        <v>0.1</v>
-      </c>
-      <c r="I2">
-        <v>0.1</v>
-      </c>
-      <c r="J2">
-        <v>0.3</v>
-      </c>
-      <c r="K2">
-        <v>0.3</v>
-      </c>
-      <c r="L2">
-        <v>0.3</v>
-      </c>
-      <c r="M2">
-        <v>0.3</v>
-      </c>
-      <c r="N2">
-        <v>0.3</v>
-      </c>
-      <c r="O2">
-        <v>0.3</v>
-      </c>
-      <c r="P2">
-        <v>0.3</v>
-      </c>
-      <c r="Q2">
-        <v>0.4</v>
-      </c>
-      <c r="R2">
-        <v>0.4</v>
-      </c>
-      <c r="S2">
-        <v>0.5</v>
-      </c>
-      <c r="T2">
-        <v>0.5</v>
-      </c>
-      <c r="U2">
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0.1</v>
+      </c>
+      <c r="H4">
+        <v>0.1</v>
+      </c>
+      <c r="I4">
+        <v>0.1</v>
+      </c>
+      <c r="J4">
+        <v>0.3</v>
+      </c>
+      <c r="K4">
+        <v>0.3</v>
+      </c>
+      <c r="L4">
+        <v>0.3</v>
+      </c>
+      <c r="M4">
+        <v>0.3</v>
+      </c>
+      <c r="N4">
+        <v>0.3</v>
+      </c>
+      <c r="O4">
         <v>0.6</v>
       </c>
-      <c r="V2">
-        <v>0.7</v>
+      <c r="P4">
+        <v>0.6</v>
+      </c>
+      <c r="Q4">
+        <v>0.6</v>
+      </c>
+      <c r="R4">
+        <v>0.6</v>
+      </c>
+      <c r="S4">
+        <v>0.9</v>
+      </c>
+      <c r="T4">
+        <v>0.9</v>
+      </c>
+      <c r="U4">
+        <v>0.9</v>
+      </c>
+      <c r="V4">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="A5">
+        <v>8</v>
+      </c>
+      <c r="B5">
+        <v>26</v>
+      </c>
+      <c r="C5">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>0.1</v>
+      </c>
+      <c r="H5">
+        <v>0.1</v>
+      </c>
+      <c r="I5">
+        <v>0.1</v>
+      </c>
+      <c r="J5">
+        <v>0.3</v>
+      </c>
+      <c r="K5">
+        <v>0.3</v>
+      </c>
+      <c r="L5">
+        <v>0.3</v>
+      </c>
+      <c r="M5">
+        <v>0.3</v>
+      </c>
+      <c r="N5">
+        <v>0.3</v>
+      </c>
+      <c r="O5">
+        <v>0.6</v>
+      </c>
+      <c r="P5">
+        <v>0.6</v>
+      </c>
+      <c r="Q5">
+        <v>0.6</v>
+      </c>
+      <c r="R5">
+        <v>0.6</v>
+      </c>
+      <c r="S5">
+        <v>0.9</v>
+      </c>
+      <c r="T5">
+        <v>0.9</v>
+      </c>
+      <c r="U5">
+        <v>0.9</v>
+      </c>
+      <c r="V5">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="A6">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.1</v>
+      </c>
+      <c r="H6">
+        <v>0.1</v>
+      </c>
+      <c r="I6">
+        <v>0.1</v>
+      </c>
+      <c r="J6">
+        <v>0.3</v>
+      </c>
+      <c r="K6">
+        <v>0.3</v>
+      </c>
+      <c r="L6">
+        <v>0.3</v>
+      </c>
+      <c r="M6">
+        <v>0.3</v>
+      </c>
+      <c r="N6">
+        <v>0.3</v>
+      </c>
+      <c r="O6">
+        <v>0.6</v>
+      </c>
+      <c r="P6">
+        <v>0.6</v>
+      </c>
+      <c r="Q6">
+        <v>0.6</v>
+      </c>
+      <c r="R6">
+        <v>0.6</v>
+      </c>
+      <c r="S6">
+        <v>0.9</v>
+      </c>
+      <c r="T6">
+        <v>0.9</v>
+      </c>
+      <c r="U6">
+        <v>0.9</v>
+      </c>
+      <c r="V6">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7">
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0.1</v>
+      </c>
+      <c r="H7">
+        <v>0.1</v>
+      </c>
+      <c r="I7">
+        <v>0.1</v>
+      </c>
+      <c r="J7">
+        <v>0.3</v>
+      </c>
+      <c r="K7">
+        <v>0.3</v>
+      </c>
+      <c r="L7">
+        <v>0.3</v>
+      </c>
+      <c r="M7">
+        <v>0.3</v>
+      </c>
+      <c r="N7">
+        <v>0.3</v>
+      </c>
+      <c r="O7">
+        <v>0.5</v>
+      </c>
+      <c r="P7">
+        <v>0.5</v>
+      </c>
+      <c r="Q7">
+        <v>0.5</v>
+      </c>
+      <c r="R7">
+        <v>0.5</v>
+      </c>
+      <c r="S7">
+        <v>0.7</v>
+      </c>
+      <c r="T7">
+        <v>0.7</v>
+      </c>
+      <c r="U7">
+        <v>0.7</v>
+      </c>
+      <c r="V7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8">
+        <v>24</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0.1</v>
+      </c>
+      <c r="H8">
+        <v>0.1</v>
+      </c>
+      <c r="I8">
+        <v>0.1</v>
+      </c>
+      <c r="J8">
+        <v>0.3</v>
+      </c>
+      <c r="K8">
+        <v>0.3</v>
+      </c>
+      <c r="L8">
+        <v>0.3</v>
+      </c>
+      <c r="M8">
+        <v>0.3</v>
+      </c>
+      <c r="N8">
+        <v>0.3</v>
+      </c>
+      <c r="O8">
+        <v>0.5</v>
+      </c>
+      <c r="P8">
+        <v>0.5</v>
+      </c>
+      <c r="Q8">
+        <v>0.5</v>
+      </c>
+      <c r="R8">
+        <v>0.5</v>
+      </c>
+      <c r="S8">
+        <v>0.7</v>
+      </c>
+      <c r="T8">
+        <v>0.7</v>
+      </c>
+      <c r="U8">
+        <v>0.7</v>
+      </c>
+      <c r="V8">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9">
+        <v>25</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0.1</v>
+      </c>
+      <c r="H9">
+        <v>0.1</v>
+      </c>
+      <c r="I9">
+        <v>0.1</v>
+      </c>
+      <c r="J9">
+        <v>0.3</v>
+      </c>
+      <c r="K9">
+        <v>0.3</v>
+      </c>
+      <c r="L9">
+        <v>0.3</v>
+      </c>
+      <c r="M9">
+        <v>0.3</v>
+      </c>
+      <c r="N9">
+        <v>0.3</v>
+      </c>
+      <c r="O9">
+        <v>0.5</v>
+      </c>
+      <c r="P9">
+        <v>0.5</v>
+      </c>
+      <c r="Q9">
+        <v>0.5</v>
+      </c>
+      <c r="R9">
+        <v>0.5</v>
+      </c>
+      <c r="S9">
+        <v>0.7</v>
+      </c>
+      <c r="T9">
+        <v>0.7</v>
+      </c>
+      <c r="U9">
+        <v>0.7</v>
+      </c>
+      <c r="V9">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>24</v>
+      </c>
+      <c r="C10">
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0.3</v>
+      </c>
+      <c r="F10">
+        <v>0.3</v>
+      </c>
+      <c r="G10">
+        <v>0.3</v>
+      </c>
+      <c r="H10">
+        <v>0.3</v>
+      </c>
+      <c r="I10">
+        <v>0.3</v>
+      </c>
+      <c r="J10">
+        <v>0.3</v>
+      </c>
+      <c r="K10">
+        <v>0.3</v>
+      </c>
+      <c r="L10">
+        <v>0.5</v>
+      </c>
+      <c r="M10">
+        <v>0.5</v>
+      </c>
+      <c r="N10">
+        <v>0.5</v>
+      </c>
+      <c r="O10">
+        <v>0.5</v>
+      </c>
+      <c r="P10">
+        <v>0.5</v>
+      </c>
+      <c r="Q10">
+        <v>0.5</v>
+      </c>
+      <c r="R10">
+        <v>0.5</v>
+      </c>
+      <c r="S10">
+        <v>0.7</v>
+      </c>
+      <c r="T10">
+        <v>0.7</v>
+      </c>
+      <c r="U10">
+        <v>0.8</v>
+      </c>
+      <c r="V10">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>25</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <v>0.3</v>
+      </c>
+      <c r="F11">
+        <v>0.3</v>
+      </c>
+      <c r="G11">
+        <v>0.3</v>
+      </c>
+      <c r="H11">
+        <v>0.3</v>
+      </c>
+      <c r="I11">
+        <v>0.3</v>
+      </c>
+      <c r="J11">
+        <v>0.3</v>
+      </c>
+      <c r="K11">
+        <v>0.3</v>
+      </c>
+      <c r="L11">
+        <v>0.5</v>
+      </c>
+      <c r="M11">
+        <v>0.5</v>
+      </c>
+      <c r="N11">
+        <v>0.5</v>
+      </c>
+      <c r="O11">
+        <v>0.5</v>
+      </c>
+      <c r="P11">
+        <v>0.5</v>
+      </c>
+      <c r="Q11">
+        <v>0.5</v>
+      </c>
+      <c r="R11">
+        <v>0.5</v>
+      </c>
+      <c r="S11">
+        <v>0.7</v>
+      </c>
+      <c r="T11">
+        <v>0.7</v>
+      </c>
+      <c r="U11">
+        <v>0.8</v>
+      </c>
+      <c r="V11">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>24</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0.3</v>
+      </c>
+      <c r="F12">
+        <v>0.3</v>
+      </c>
+      <c r="G12">
+        <v>0.3</v>
+      </c>
+      <c r="H12">
+        <v>0.3</v>
+      </c>
+      <c r="I12">
+        <v>0.3</v>
+      </c>
+      <c r="J12">
+        <v>0.3</v>
+      </c>
+      <c r="K12">
+        <v>0.3</v>
+      </c>
+      <c r="L12">
+        <v>0.5</v>
+      </c>
+      <c r="M12">
+        <v>0.5</v>
+      </c>
+      <c r="N12">
+        <v>0.5</v>
+      </c>
+      <c r="O12">
+        <v>0.5</v>
+      </c>
+      <c r="P12">
+        <v>0.5</v>
+      </c>
+      <c r="Q12">
+        <v>0.5</v>
+      </c>
+      <c r="R12">
+        <v>0.5</v>
+      </c>
+      <c r="S12">
+        <v>0.7</v>
+      </c>
+      <c r="T12">
+        <v>0.7</v>
+      </c>
+      <c r="U12">
+        <v>0.8</v>
+      </c>
+      <c r="V12">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <v>25</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <v>0.3</v>
+      </c>
+      <c r="F13">
+        <v>0.3</v>
+      </c>
+      <c r="G13">
+        <v>0.3</v>
+      </c>
+      <c r="H13">
+        <v>0.3</v>
+      </c>
+      <c r="I13">
+        <v>0.3</v>
+      </c>
+      <c r="J13">
+        <v>0.3</v>
+      </c>
+      <c r="K13">
+        <v>0.3</v>
+      </c>
+      <c r="L13">
+        <v>0.5</v>
+      </c>
+      <c r="M13">
+        <v>0.5</v>
+      </c>
+      <c r="N13">
+        <v>0.5</v>
+      </c>
+      <c r="O13">
+        <v>0.5</v>
+      </c>
+      <c r="P13">
+        <v>0.5</v>
+      </c>
+      <c r="Q13">
+        <v>0.5</v>
+      </c>
+      <c r="R13">
+        <v>0.5</v>
+      </c>
+      <c r="S13">
+        <v>0.7</v>
+      </c>
+      <c r="T13">
+        <v>0.7</v>
+      </c>
+      <c r="U13">
+        <v>0.8</v>
+      </c>
+      <c r="V13">
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/SType3.xlsx
+++ b/SType3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_LASSO\LAS_Simulation_Jateng\I-O_Analysis\Regional-Economy---Jawa-Tengah\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/d_bodro_landscapealliance_org/Documents/Documents/GitHub/Regional-Economy---Jawa-Tengah/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{096EDC42-F7B0-49C2-ACC4-A602AA5AD75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{096EDC42-F7B0-49C2-ACC4-A602AA5AD75A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{224767FF-C9D7-44C9-8D0A-62ADBE84ABFB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6004D651-5FD1-4A47-B3D1-E1DB32589301}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6004D651-5FD1-4A47-B3D1-E1DB32589301}"/>
   </bookViews>
   <sheets>
     <sheet name="SType3" sheetId="1" r:id="rId1"/>
@@ -36,6 +36,17 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>FROM</t>
+  </si>
+  <si>
+    <t>TO</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -234,75 +245,75 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12A33DC9-E3CC-4C63-BB30-F93F101A1549}">
-  <dimension ref="A1:V13"/>
-  <sheetFormatPr defaultRowHeight="14"/>
+  <dimension ref="A1:V14"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="1" spans="1:22">
-      <c r="A1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>1</v>
+      </c>
+      <c r="D1">
+        <v>2</v>
+      </c>
+      <c r="E1">
+        <v>3</v>
+      </c>
+      <c r="F1">
+        <v>4</v>
+      </c>
+      <c r="G1">
+        <v>5</v>
+      </c>
+      <c r="H1">
+        <v>6</v>
+      </c>
+      <c r="I1">
         <v>7</v>
       </c>
-      <c r="B1">
-        <v>24</v>
-      </c>
-      <c r="C1">
-        <v>0</v>
-      </c>
-      <c r="D1">
-        <v>0</v>
-      </c>
-      <c r="E1">
-        <v>0</v>
-      </c>
-      <c r="F1">
-        <v>0</v>
-      </c>
-      <c r="G1">
-        <v>0.1</v>
-      </c>
-      <c r="H1">
-        <v>0.1</v>
-      </c>
-      <c r="I1">
-        <v>0.1</v>
-      </c>
       <c r="J1">
-        <v>0.1</v>
+        <v>8</v>
       </c>
       <c r="K1">
-        <v>0.1</v>
+        <v>9</v>
       </c>
       <c r="L1">
-        <v>0.2</v>
+        <v>10</v>
       </c>
       <c r="M1">
-        <v>0.2</v>
+        <v>11</v>
       </c>
       <c r="N1">
-        <v>0.2</v>
+        <v>12</v>
       </c>
       <c r="O1">
-        <v>0.7</v>
+        <v>13</v>
       </c>
       <c r="P1">
-        <v>0.7</v>
+        <v>14</v>
       </c>
       <c r="Q1">
-        <v>0.7</v>
+        <v>15</v>
       </c>
       <c r="R1">
-        <v>0.9</v>
+        <v>16</v>
       </c>
       <c r="S1">
-        <v>0.9</v>
+        <v>17</v>
       </c>
       <c r="T1">
-        <v>0.9</v>
+        <v>18</v>
       </c>
       <c r="U1">
-        <v>0.9</v>
+        <v>19</v>
       </c>
       <c r="V1">
-        <v>0.9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:22">
@@ -310,7 +321,7 @@
         <v>7</v>
       </c>
       <c r="B2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -378,7 +389,7 @@
         <v>7</v>
       </c>
       <c r="B3">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -443,10 +454,10 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -470,31 +481,31 @@
         <v>0.1</v>
       </c>
       <c r="J4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="K4">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="L4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N4">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="O4">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="P4">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="Q4">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="R4">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="S4">
         <v>0.9</v>
@@ -514,7 +525,7 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -582,7 +593,7 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -647,10 +658,10 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="B7">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C7">
         <v>0</v>
@@ -689,28 +700,28 @@
         <v>0.3</v>
       </c>
       <c r="O7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="P7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="Q7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="R7">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="S7">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="T7">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="U7">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="V7">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="8" spans="1:22">
@@ -718,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B8">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -786,7 +797,7 @@
         <v>1</v>
       </c>
       <c r="B9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -851,10 +862,10 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="B10">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -863,19 +874,19 @@
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="G10">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="H10">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I10">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="J10">
         <v>0.3</v>
@@ -884,13 +895,13 @@
         <v>0.3</v>
       </c>
       <c r="L10">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="M10">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N10">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O10">
         <v>0.5</v>
@@ -911,10 +922,10 @@
         <v>0.7</v>
       </c>
       <c r="U10">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="V10">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -922,7 +933,7 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11">
         <v>0</v>
@@ -987,10 +998,10 @@
     </row>
     <row r="12" spans="1:22">
       <c r="A12">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1058,7 +1069,7 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1118,6 +1129,74 @@
         <v>0.8</v>
       </c>
       <c r="V13">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>25</v>
+      </c>
+      <c r="C14">
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <v>0.3</v>
+      </c>
+      <c r="F14">
+        <v>0.3</v>
+      </c>
+      <c r="G14">
+        <v>0.3</v>
+      </c>
+      <c r="H14">
+        <v>0.3</v>
+      </c>
+      <c r="I14">
+        <v>0.3</v>
+      </c>
+      <c r="J14">
+        <v>0.3</v>
+      </c>
+      <c r="K14">
+        <v>0.3</v>
+      </c>
+      <c r="L14">
+        <v>0.5</v>
+      </c>
+      <c r="M14">
+        <v>0.5</v>
+      </c>
+      <c r="N14">
+        <v>0.5</v>
+      </c>
+      <c r="O14">
+        <v>0.5</v>
+      </c>
+      <c r="P14">
+        <v>0.5</v>
+      </c>
+      <c r="Q14">
+        <v>0.5</v>
+      </c>
+      <c r="R14">
+        <v>0.5</v>
+      </c>
+      <c r="S14">
+        <v>0.7</v>
+      </c>
+      <c r="T14">
+        <v>0.7</v>
+      </c>
+      <c r="U14">
+        <v>0.8</v>
+      </c>
+      <c r="V14">
         <v>0.8</v>
       </c>
     </row>
